--- a/docs/package/02_Commercials/iNXT_BrokerVerse_Price_Book.xlsx
+++ b/docs/package/02_Commercials/iNXT_BrokerVerse_Price_Book.xlsx
@@ -59,6 +59,12 @@
     <definedName name="Int_Cx">'Price Basis'!$B$73</definedName>
     <definedName name="LOB_After">'Price Basis'!$B$74</definedName>
     <definedName name="Report_Item">'Price Basis'!$B$75</definedName>
+    <definedName name="Conn_Golive">'Price Basis'!$B$76</definedName>
+    <definedName name="AML_Act">'Price Basis'!$B$77</definedName>
+    <definedName name="IC_Act">'Price Basis'!$B$78</definedName>
+    <definedName name="BIR_Act">'Price Basis'!$B$79</definedName>
+    <definedName name="Dealer_Prog">'Price Basis'!$B$80</definedName>
+    <definedName name="Brand_Pack">'Price Basis'!$B$81</definedName>
     <definedName name="Disc_AM">Negotiation!$B$6</definedName>
     <definedName name="Disc_SH">Negotiation!$C$6</definedName>
     <definedName name="Disc_CEO">Negotiation!$D$6</definedName>
@@ -16027,7 +16033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -17663,37 +17669,127 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Training beyond the included days</t>
-        </is>
-      </c>
-      <c r="B76" s="19">
-        <f>Rate_Trainer</f>
-        <v/>
+          <t>Connector go-live with a partner (to confirm by management)</t>
+        </is>
+      </c>
+      <c r="B76" s="35" t="n">
+        <v>80000</v>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>per trainer day</t>
+          <t>per connector</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
+          <t>Activation of the AML/CFT toolkit (to confirm by management)</t>
+        </is>
+      </c>
+      <c r="B77" s="35" t="n">
+        <v>130000</v>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>Activation of the IC compliance registers (to confirm by management)</t>
+        </is>
+      </c>
+      <c r="B78" s="35" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>Activation of the BIR pack (to confirm by management)</t>
+        </is>
+      </c>
+      <c r="B79" s="35" t="n">
+        <v>130000</v>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>Dealer programme set-up (to confirm by management)</t>
+        </is>
+      </c>
+      <c r="B80" s="35" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>per programme</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Client brand pack (to confirm by management)</t>
+        </is>
+      </c>
+      <c r="B81" s="35" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Training beyond the included days</t>
+        </is>
+      </c>
+      <c r="B82" s="19">
+        <f>Rate_Trainer</f>
+        <v/>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>per trainer day</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
           <t>On-site consultant day (Metro Manila)</t>
         </is>
       </c>
-      <c r="B77" s="19">
+      <c r="B83" s="19">
         <f>Rate_Onsite</f>
         <v/>
       </c>
-      <c r="C77" s="10" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>per day</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="23" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="23" t="inlineStr">
         <is>
           <t>Read from BrokerVerse_Commercials_and_Pricing.xlsx (recommended price points) when this book was built. Pricing workbook state: recalculated with LibreOffice before reading.</t>
         </is>
@@ -17709,8 +17805,8 @@
     <mergeCell ref="D17:L17"/>
     <mergeCell ref="D16:L16"/>
     <mergeCell ref="D7:L7"/>
+    <mergeCell ref="A85:L85"/>
     <mergeCell ref="D18:L18"/>
-    <mergeCell ref="A79:L79"/>
     <mergeCell ref="D9:L9"/>
     <mergeCell ref="D12:L12"/>
     <mergeCell ref="D8:L8"/>

--- a/docs/package/02_Commercials/iNXT_BrokerVerse_Price_Book.xlsx
+++ b/docs/package/02_Commercials/iNXT_BrokerVerse_Price_Book.xlsx
@@ -59,12 +59,22 @@
     <definedName name="Int_Cx">'Price Basis'!$B$73</definedName>
     <definedName name="LOB_After">'Price Basis'!$B$74</definedName>
     <definedName name="Report_Item">'Price Basis'!$B$75</definedName>
-    <definedName name="Conn_Golive">'Price Basis'!$B$76</definedName>
-    <definedName name="AML_Act">'Price Basis'!$B$77</definedName>
-    <definedName name="IC_Act">'Price Basis'!$B$78</definedName>
-    <definedName name="BIR_Act">'Price Basis'!$B$79</definedName>
-    <definedName name="Dealer_Prog">'Price Basis'!$B$80</definedName>
-    <definedName name="Brand_Pack">'Price Basis'!$B$81</definedName>
+    <definedName name="Conn_Golive">'Price Basis'!$B$81</definedName>
+    <definedName name="AML_Act">'Price Basis'!$B$82</definedName>
+    <definedName name="IC_Act">'Price Basis'!$B$83</definedName>
+    <definedName name="BIR_Act">'Price Basis'!$B$84</definedName>
+    <definedName name="Dealer_Prog">'Price Basis'!$B$85</definedName>
+    <definedName name="Brand_Pack">'Price Basis'!$B$86</definedName>
+    <definedName name="AMLC_Val">'Price Basis'!$B$87</definedName>
+    <definedName name="IC_Form">'Price Basis'!$B$88</definedName>
+    <definedName name="EOPT_Rev">'Price Basis'!$B$89</definedName>
+    <definedName name="CAS_Reg">'Price Basis'!$B$90</definedName>
+    <definedName name="EIS_Enrol">'Price Basis'!$B$91</definedName>
+    <definedName name="CTPL_Cert">'Price Basis'!$B$92</definedName>
+    <definedName name="Insurer_Onb">'Price Basis'!$B$93</definedName>
+    <definedName name="Bank_Cert">'Price Basis'!$B$94</definedName>
+    <definedName name="SMS_Act">'Price Basis'!$B$95</definedName>
+    <definedName name="Screen_Prov">'Price Basis'!$B$96</definedName>
     <definedName name="Disc_AM">Negotiation!$B$6</definedName>
     <definedName name="Disc_SH">Negotiation!$C$6</definedName>
     <definedName name="Disc_CEO">Negotiation!$D$6</definedName>
@@ -672,7 +682,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>iorta TechNXT Corp. Prepared 03 October 2026. INTERNAL: contains discount limits and floor prices. Do not send this workbook to a client.</t>
+          <t>iorta TechNXT Corp. Prepared 03 October 2026, revised 04 October 2026 (optional modules and partner services confirmed). INTERNAL: contains discount limits and floor prices. Do not send this workbook to a client.</t>
         </is>
       </c>
     </row>
@@ -16033,7 +16043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -17669,127 +17679,365 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Connector go-live with a partner (to confirm by management)</t>
-        </is>
-      </c>
-      <c r="B76" s="35" t="n">
-        <v>80000</v>
+          <t>Training beyond the included days</t>
+        </is>
+      </c>
+      <c r="B76" s="19">
+        <f>Rate_Trainer</f>
+        <v/>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>per connector</t>
+          <t>per trainer day</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Activation of the AML/CFT toolkit (to confirm by management)</t>
-        </is>
-      </c>
-      <c r="B77" s="35" t="n">
-        <v>130000</v>
+          <t>On-site consultant day (Metro Manila)</t>
+        </is>
+      </c>
+      <c r="B77" s="19">
+        <f>Rate_Onsite</f>
+        <v/>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>one-time</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>Activation of the IC compliance registers (to confirm by management)</t>
-        </is>
-      </c>
-      <c r="B78" s="35" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>one-time</t>
+          <t>per day</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Activation of the BIR pack (to confirm by management)</t>
-        </is>
-      </c>
-      <c r="B79" s="35" t="n">
-        <v>130000</v>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>one-time</t>
-        </is>
-      </c>
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Optional modules and partner services (PHP): add-on items confirmed by management on 04 October 2026; the regulator's or partner's own fees are not included</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="7" t="n"/>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="7" t="n"/>
+      <c r="G79" s="7" t="n"/>
+      <c r="H79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
+      <c r="J79" s="7" t="n"/>
+      <c r="K79" s="7" t="n"/>
+      <c r="L79" s="7" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>Dealer programme set-up (to confirm by management)</t>
-        </is>
-      </c>
-      <c r="B80" s="35" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>per programme</t>
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Man-days</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Client brand pack (to confirm by management)</t>
+          <t>Connector go-live with a partner</t>
         </is>
       </c>
       <c r="B81" s="35" t="n">
-        <v>30000</v>
+        <v>80000</v>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>per pack</t>
-        </is>
+          <t>per connector</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>Training beyond the included days</t>
-        </is>
-      </c>
-      <c r="B82" s="19">
-        <f>Rate_Trainer</f>
-        <v/>
+          <t>Activation of the AML/CFT toolkit</t>
+        </is>
+      </c>
+      <c r="B82" s="35" t="n">
+        <v>130000</v>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>per trainer day</t>
-        </is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>On-site consultant day (Metro Manila)</t>
-        </is>
-      </c>
-      <c r="B83" s="19">
-        <f>Rate_Onsite</f>
-        <v/>
+          <t>Activation of the IC compliance registers</t>
+        </is>
+      </c>
+      <c r="B83" s="35" t="n">
+        <v>100000</v>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>per day</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="A85" s="23" t="inlineStr">
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Activation of the BIR pack</t>
+        </is>
+      </c>
+      <c r="B84" s="35" t="n">
+        <v>130000</v>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Dealer programme set-up</t>
+        </is>
+      </c>
+      <c r="B85" s="35" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>per programme</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>Client brand pack</t>
+        </is>
+      </c>
+      <c r="B86" s="35" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>per pack</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>AMLC reporting file validation and portal test</t>
+        </is>
+      </c>
+      <c r="B87" s="35" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>IC annual statement form alignment</t>
+        </is>
+      </c>
+      <c r="B88" s="35" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>EOPT invoicing review with the broker tax adviser</t>
+        </is>
+      </c>
+      <c r="B89" s="35" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>BIR CAS registration support</t>
+        </is>
+      </c>
+      <c r="B90" s="35" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="D90" s="24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>BIR EIS enrolment and certification</t>
+        </is>
+      </c>
+      <c r="B91" s="35" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>CTPL authentication and LTO interface certification</t>
+        </is>
+      </c>
+      <c r="B92" s="35" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="D92" s="24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>Insurer API onboarding, per insurer</t>
+        </is>
+      </c>
+      <c r="B93" s="35" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>per insurer</t>
+        </is>
+      </c>
+      <c r="D93" s="24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>Bank payment file certification, per bank</t>
+        </is>
+      </c>
+      <c r="B94" s="35" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>per bank</t>
+        </is>
+      </c>
+      <c r="D94" s="24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>SMS or Viber gateway activation</t>
+        </is>
+      </c>
+      <c r="B95" s="35" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="D95" s="24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>Screening list provider onboarding</t>
+        </is>
+      </c>
+      <c r="B96" s="35" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="D96" s="24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="23" t="inlineStr">
         <is>
           <t>Read from BrokerVerse_Commercials_and_Pricing.xlsx (recommended price points) when this book was built. Pricing workbook state: recalculated with LibreOffice before reading.</t>
         </is>
@@ -17805,7 +18053,6 @@
     <mergeCell ref="D17:L17"/>
     <mergeCell ref="D16:L16"/>
     <mergeCell ref="D7:L7"/>
-    <mergeCell ref="A85:L85"/>
     <mergeCell ref="D18:L18"/>
     <mergeCell ref="D9:L9"/>
     <mergeCell ref="D12:L12"/>
@@ -17823,6 +18070,7 @@
     <mergeCell ref="D10:L10"/>
     <mergeCell ref="D19:L19"/>
     <mergeCell ref="A64:L64"/>
+    <mergeCell ref="A98:L98"/>
     <mergeCell ref="F41:L41"/>
     <mergeCell ref="D22:L22"/>
     <mergeCell ref="F38:L38"/>
